--- a/applications/tracking_disturbance_3species_reinforce/Discover_Molecular_Integrators_REINFORCE.xlsx
+++ b/applications/tracking_disturbance_3species_reinforce/Discover_Molecular_Integrators_REINFORCE.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,19 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,14 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,31 +44,13 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -159,10 +129,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -200,71 +170,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -288,53 +256,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -344,7 +313,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -353,7 +322,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -362,7 +331,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -370,10 +339,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -402,7 +371,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -415,12 +384,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -440,91 +410,366 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:AH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.005" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
-    <col width="13.005" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
-    <col width="13.005" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>2025-06-12 22:21:48</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>2025-06-13 08:27:22</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2025-09-11 09:26:07</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025-09-12 10:58:59</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2025-06-13 11:03:04</t>
+          <t>2025-09-12 10:59:54</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2025-06-13 11:57:35</t>
+          <t>2025-09-12 11:05:47</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2025-06-13 13:37:08</t>
+          <t>2025-09-12 11:06:55</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:07:59</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:11:00</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:17:55</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:19:22</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:20:11</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:20:31</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:24:27</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:47:28</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:51:11</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:52:40</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2025-09-12 11:57:08</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2025-09-12 13:42:37</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2025-09-12 13:57:39</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2025-09-12 14:03:59</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2025-09-12 14:07:51</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2025-09-12 15:47:52</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2025-09-12 15:51:55</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2025-09-12 16:24:55</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2025-09-12 16:29:41</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2025-09-12 16:46:42</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2025-09-12 16:55:34</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2025-09-12 17:05:14</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2025-09-12 17:21:01</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2025-09-12 17:30:23</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2025-09-15 09:25:09</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2025-09-15 09:28:02</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2025-09-15 09:28:58</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2025-09-15 09:30:03</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.comet.com/maurice-filo/molecular-integrators/86e1566278d044cf98671fad0776a233</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.comet.com/maurice-filo/molecular-integrators/bfbaa9ca20614a01889f9ab2f4d71b5e</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/380ed8e543054e4c92b69d3c2f25946a</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/16721f88ee8d41b5bbac00d826185db3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.comet.com/maurice-filo/molecular-integrators/ac923157a9984500b13c2249ca86d72f</t>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/b026cc801c5c43fbba9d28479fa25aa6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.comet.com/maurice-filo/molecular-integrators/e26eb0ba90db47ba935b04d8860b7bcf</t>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/a62074731475416b90ece607ebbd9463</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.comet.com/maurice-filo/molecular-integrators/b4fe07796d264cc7be7bde47a3aa2980</t>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/a62074731475416b90ece607ebbd9463</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/d5481071662c4c5398a01e261c070b4b</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/100dc4917e224596801cb668906dba47</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/0a947b4ad2db4bf9ac17965b88c3062c</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/0113b509d0c94156af36753c9ea6b468</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/ac63006dedc24ea487390fedcdeb5c39</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/024394fe19a4456d8ba3de9ddc543517</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/b224f62ee4394eb5a8c11b861d687091</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/b25793f743e34ff7a8b9c779257be752</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/f66762d3ff8d49e78b9f403ac53fb394</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/01d19fbc64904ec2ab562c12b1dcc255</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/1cb3b5dd84594e3c90f76158e0479138</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/a1367e1c84da479ca3be5ad73e2c892a</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/c3bae876bd514c20bb6f891aa2f1e62e</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/c01001e151114b268ee51cc10224d8b2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/a1456924b9634ec4a8ae4d5fd40ed40f</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/7d5966928c3c427883d9208aacf9368f</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/9eb64d2b7ee44310bbfb8b18e86dec9a</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/ed316345b53945bfbcc207032dbd1275</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/5c8a946c423843f8b535477847edfcdf</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/8da867b3b08a4fd7bd4392cec17e2c9e</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/3a841980a36847bcb73d6ffa1fec7e72</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/0bd97b974df848aca58348c3888fe541</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/194c1263bc1e4c46afb069682d7c0453</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/3a7c738f4aa247f1b0bfa764e4c698af</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/a162fefcf7414ef2af665ed16caae876</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/58b5249b96e34ace8f2dbdc71e7b2f66</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/aa32f5e72add46b2ac36c24fc32a72e4</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/ea4d8f4f3b0e44399119ca3814b678d7</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Maximum Number of Reactions</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
@@ -536,17 +781,101 @@
       <c r="F3" t="n">
         <v>5</v>
       </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Number of Species</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
@@ -558,17 +887,101 @@
       <c r="F4" t="n">
         <v>3</v>
       </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Number of Inputs</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" t="n">
         <v>2</v>
       </c>
       <c r="D5" t="n">
@@ -580,17 +993,101 @@
       <c r="F5" t="n">
         <v>2</v>
       </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Batch Size</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" t="n">
         <v>1280</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" t="n">
         <v>1280</v>
       </c>
       <c r="D6" t="n">
@@ -602,17 +1099,101 @@
       <c r="F6" t="n">
         <v>1280</v>
       </c>
+      <c r="G6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1280</v>
+      </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Allow Input Influence</t>
         </is>
       </c>
-      <c r="B7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="b">
+      <c r="B7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="b">
@@ -624,17 +1205,101 @@
       <c r="F7" t="b">
         <v>0</v>
       </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Learning Rate</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" t="n">
         <v>0.0001</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" t="n">
         <v>0.0001</v>
       </c>
       <c r="D8" t="n">
@@ -646,17 +1311,101 @@
       <c r="F8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Number of Epochs</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>500</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>500</v>
       </c>
       <c r="D9" t="n">
@@ -668,17 +1417,101 @@
       <c r="F9" t="n">
         <v>500</v>
       </c>
+      <c r="G9" t="n">
+        <v>500</v>
+      </c>
+      <c r="H9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>500</v>
+      </c>
+      <c r="J9" t="n">
+        <v>500</v>
+      </c>
+      <c r="K9" t="n">
+        <v>500</v>
+      </c>
+      <c r="L9" t="n">
+        <v>500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>500</v>
+      </c>
+      <c r="O9" t="n">
+        <v>500</v>
+      </c>
+      <c r="P9" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>500</v>
+      </c>
+      <c r="R9" t="n">
+        <v>500</v>
+      </c>
+      <c r="S9" t="n">
+        <v>500</v>
+      </c>
+      <c r="T9" t="n">
+        <v>500</v>
+      </c>
+      <c r="U9" t="n">
+        <v>500</v>
+      </c>
+      <c r="V9" t="n">
+        <v>500</v>
+      </c>
+      <c r="W9" t="n">
+        <v>500</v>
+      </c>
+      <c r="X9" t="n">
+        <v>500</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>500</v>
+      </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Neural Network Depth</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
@@ -690,17 +1523,101 @@
       <c r="F10" t="n">
         <v>5</v>
       </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Neural Network Width</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>1024</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" t="n">
         <v>1024</v>
       </c>
       <c r="D11" t="n">
@@ -712,17 +1629,101 @@
       <c r="F11" t="n">
         <v>1024</v>
       </c>
+      <c r="G11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1024</v>
+      </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Deep Layer Size</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" t="n">
         <v>10240</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" t="n">
         <v>10240</v>
       </c>
       <c r="D12" t="n">
@@ -734,17 +1735,101 @@
       <c r="F12" t="n">
         <v>10240</v>
       </c>
+      <c r="G12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="V12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="W12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>10240</v>
+      </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Number of CPUs</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>128</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="n">
         <v>128</v>
       </c>
       <c r="D13" t="n">
@@ -756,18 +1841,102 @@
       <c r="F13" t="n">
         <v>128</v>
       </c>
+      <c r="G13" t="n">
+        <v>128</v>
+      </c>
+      <c r="H13" t="n">
+        <v>128</v>
+      </c>
+      <c r="I13" t="n">
+        <v>128</v>
+      </c>
+      <c r="J13" t="n">
+        <v>128</v>
+      </c>
+      <c r="K13" t="n">
+        <v>128</v>
+      </c>
+      <c r="L13" t="n">
+        <v>128</v>
+      </c>
+      <c r="M13" t="n">
+        <v>128</v>
+      </c>
+      <c r="N13" t="n">
+        <v>128</v>
+      </c>
+      <c r="O13" t="n">
+        <v>128</v>
+      </c>
+      <c r="P13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>128</v>
+      </c>
+      <c r="R13" t="n">
+        <v>128</v>
+      </c>
+      <c r="S13" t="n">
+        <v>128</v>
+      </c>
+      <c r="T13" t="n">
+        <v>128</v>
+      </c>
+      <c r="U13" t="n">
+        <v>128</v>
+      </c>
+      <c r="V13" t="n">
+        <v>128</v>
+      </c>
+      <c r="W13" t="n">
+        <v>128</v>
+      </c>
+      <c r="X13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>128</v>
+      </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Initial Entropy Weight</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>10</v>
+      <c r="B14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" t="n">
+        <v>50</v>
       </c>
       <c r="D14" t="n">
         <v>50</v>
@@ -778,17 +1947,101 @@
       <c r="F14" t="n">
         <v>50</v>
       </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50</v>
+      </c>
+      <c r="K14" t="n">
+        <v>50</v>
+      </c>
+      <c r="L14" t="n">
+        <v>50</v>
+      </c>
+      <c r="M14" t="n">
+        <v>50</v>
+      </c>
+      <c r="N14" t="n">
+        <v>50</v>
+      </c>
+      <c r="O14" t="n">
+        <v>50</v>
+      </c>
+      <c r="P14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>50</v>
+      </c>
+      <c r="R14" t="n">
+        <v>50</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="n">
+        <v>50</v>
+      </c>
+      <c r="U14" t="n">
+        <v>50</v>
+      </c>
+      <c r="V14" t="n">
+        <v>50</v>
+      </c>
+      <c r="W14" t="n">
+        <v>50</v>
+      </c>
+      <c r="X14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>50</v>
+      </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Entropy Update Coefficient</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" t="n">
         <v>0.75</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" t="n">
         <v>0.75</v>
       </c>
       <c r="D15" t="n">
@@ -800,17 +2053,101 @@
       <c r="F15" t="n">
         <v>0.75</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.75</v>
+      </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Entropy Schedule</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
@@ -822,21 +2159,105 @@
       <c r="F16" t="n">
         <v>5</v>
       </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>5</v>
+      </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Minimum Entropy Weight</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1</v>
+      <c r="B17" t="n">
+        <v>50</v>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
         <v>50</v>
@@ -844,39 +2265,207 @@
       <c r="F17" t="n">
         <v>50</v>
       </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" t="n">
+        <v>50</v>
+      </c>
+      <c r="M17" t="n">
+        <v>50</v>
+      </c>
+      <c r="N17" t="n">
+        <v>50</v>
+      </c>
+      <c r="O17" t="n">
+        <v>50</v>
+      </c>
+      <c r="P17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" t="n">
+        <v>50</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="n">
+        <v>50</v>
+      </c>
+      <c r="U17" t="n">
+        <v>50</v>
+      </c>
+      <c r="V17" t="n">
+        <v>50</v>
+      </c>
+      <c r="W17" t="n">
+        <v>50</v>
+      </c>
+      <c r="X17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>50</v>
+      </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0.9</v>
+      <c r="B18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.95</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="F18" t="n">
         <v>0.95</v>
       </c>
+      <c r="G18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.95</v>
+      </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Risk Update</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
@@ -888,17 +2477,101 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Maximum Risk</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
@@ -910,17 +2583,101 @@
       <c r="F20" t="n">
         <v>1</v>
       </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Risk Schedule</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" t="n">
         <v>20</v>
       </c>
       <c r="D21" t="n">
@@ -932,17 +2689,101 @@
       <c r="F21" t="n">
         <v>20</v>
       </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20</v>
+      </c>
+      <c r="K21" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20</v>
+      </c>
+      <c r="N21" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P21" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>20</v>
+      </c>
+      <c r="R21" t="n">
+        <v>20</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="n">
+        <v>20</v>
+      </c>
+      <c r="U21" t="n">
+        <v>20</v>
+      </c>
+      <c r="V21" t="n">
+        <v>20</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>20</v>
+      </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Render Schedule</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
@@ -954,17 +2795,101 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Hall of Fame Size</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" t="n">
         <v>10</v>
       </c>
       <c r="D23" t="n">
@@ -976,17 +2901,101 @@
       <c r="F23" t="n">
         <v>10</v>
       </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>10</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>10</v>
+      </c>
+      <c r="U23" t="n">
+        <v>10</v>
+      </c>
+      <c r="V23" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" t="n">
+        <v>10</v>
+      </c>
+      <c r="X23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>10</v>
+      </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Simulation Time</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" t="n">
         <v>200</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" t="n">
         <v>200</v>
       </c>
       <c r="D24" t="n">
@@ -998,17 +3007,101 @@
       <c r="F24" t="n">
         <v>200</v>
       </c>
+      <c r="G24" t="n">
+        <v>200</v>
+      </c>
+      <c r="H24" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" t="n">
+        <v>200</v>
+      </c>
+      <c r="J24" t="n">
+        <v>200</v>
+      </c>
+      <c r="K24" t="n">
+        <v>200</v>
+      </c>
+      <c r="L24" t="n">
+        <v>200</v>
+      </c>
+      <c r="M24" t="n">
+        <v>200</v>
+      </c>
+      <c r="N24" t="n">
+        <v>200</v>
+      </c>
+      <c r="O24" t="n">
+        <v>200</v>
+      </c>
+      <c r="P24" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>200</v>
+      </c>
+      <c r="R24" t="n">
+        <v>200</v>
+      </c>
+      <c r="S24" t="n">
+        <v>200</v>
+      </c>
+      <c r="T24" t="n">
+        <v>200</v>
+      </c>
+      <c r="U24" t="n">
+        <v>200</v>
+      </c>
+      <c r="V24" t="n">
+        <v>200</v>
+      </c>
+      <c r="W24" t="n">
+        <v>200</v>
+      </c>
+      <c r="X24" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>200</v>
+      </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Number of Time Steps</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" t="n">
         <v>1000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" t="n">
         <v>1000</v>
       </c>
       <c r="D25" t="n">
@@ -1020,17 +3113,101 @@
       <c r="F25" t="n">
         <v>1000</v>
       </c>
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Initial Condition Scenarios</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3" t="n">
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
@@ -1042,17 +3219,101 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Input Scenarios</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" t="n">
         <v>9</v>
       </c>
       <c r="D27" t="n">
@@ -1064,8 +3325,92 @@
       <c r="F27" t="n">
         <v>9</v>
       </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>9</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9</v>
+      </c>
+      <c r="M27" t="n">
+        <v>9</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>9</v>
+      </c>
+      <c r="R27" t="n">
+        <v>9</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T27" t="n">
+        <v>9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>9</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>9</v>
+      </c>
+      <c r="X27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/applications/tracking_disturbance_3species_reinforce/Discover_Molecular_Integrators_REINFORCE.xlsx
+++ b/applications/tracking_disturbance_3species_reinforce/Discover_Molecular_Integrators_REINFORCE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH27"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,81 @@
           <t>2025-09-15 09:30:03</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2025-09-15 09:59:44</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:11:40</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:15:06</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:15:43</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:19:03</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:32:35</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:33:05</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:33:40</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2025-09-15 10:37:47</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2025-09-15 13:36:16</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2025-09-15 13:36:30</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2025-09-15 13:37:14</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2025-09-15 13:40:00</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2025-09-15 13:42:12</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2025-09-15 13:49:14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -759,6 +834,81 @@
           <t>https://www.comet.com/maurice-filo/molecular-integrators/ea4d8f4f3b0e44399119ca3814b678d7</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/4b708de3411745469c997df7afaed569</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/e88215bdd548403091bdfd5a8bc6194d</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/da4388ed83e1412fbd26fbafbf7945b3</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/c84577775ea444c787dc5e7a2dc651fd</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/b5323f913ba24f2297f27bd1798475b7</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/65e71c3577c44bbd8ae9342e6556ac17</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/bdc5effe74954cec9eb3cda52cf6a85f</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/c5dc6a82f53642118842a581333f9fbd</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/78cd3977fcba4220a16f5ffbd97b7edd</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/9d6d02be275f4eb0840e2d059e7398e4</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/1ec320ae5e1a488c8eb2c0e47b953ce5</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/d0cdc579031f4a0185b0cdfe6ac291e7</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/e85fc51a0ccf4f5a981d250ade24ebc4</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/33efb0ae3b754af68a0af369020e51b0</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/e64f49daac3a4bc28d80af1d4c31a23a</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -865,6 +1015,51 @@
       <c r="AH3" t="n">
         <v>5</v>
       </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -971,6 +1166,51 @@
       <c r="AH4" t="n">
         <v>3</v>
       </c>
+      <c r="AI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1077,6 +1317,51 @@
       <c r="AH5" t="n">
         <v>2</v>
       </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1183,6 +1468,51 @@
       <c r="AH6" t="n">
         <v>1280</v>
       </c>
+      <c r="AI6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1289,6 +1619,51 @@
       <c r="AH7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1395,6 +1770,51 @@
       <c r="AH8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AI8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1501,6 +1921,51 @@
       <c r="AH9" t="n">
         <v>500</v>
       </c>
+      <c r="AI9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1607,6 +2072,51 @@
       <c r="AH10" t="n">
         <v>5</v>
       </c>
+      <c r="AI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1713,6 +2223,51 @@
       <c r="AH11" t="n">
         <v>1024</v>
       </c>
+      <c r="AI11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1819,6 +2374,51 @@
       <c r="AH12" t="n">
         <v>10240</v>
       </c>
+      <c r="AI12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1925,6 +2525,51 @@
       <c r="AH13" t="n">
         <v>128</v>
       </c>
+      <c r="AI13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2031,6 +2676,51 @@
       <c r="AH14" t="n">
         <v>50</v>
       </c>
+      <c r="AI14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2137,6 +2827,51 @@
       <c r="AH15" t="n">
         <v>0.75</v>
       </c>
+      <c r="AI15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2243,6 +2978,51 @@
       <c r="AH16" t="n">
         <v>5</v>
       </c>
+      <c r="AI16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2349,6 +3129,51 @@
       <c r="AH17" t="n">
         <v>50</v>
       </c>
+      <c r="AI17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2455,6 +3280,51 @@
       <c r="AH18" t="n">
         <v>0.95</v>
       </c>
+      <c r="AI18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2561,6 +3431,51 @@
       <c r="AH19" t="n">
         <v>0</v>
       </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2667,6 +3582,51 @@
       <c r="AH20" t="n">
         <v>1</v>
       </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2773,6 +3733,51 @@
       <c r="AH21" t="n">
         <v>20</v>
       </c>
+      <c r="AI21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2879,6 +3884,51 @@
       <c r="AH22" t="n">
         <v>1</v>
       </c>
+      <c r="AI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2985,6 +4035,51 @@
       <c r="AH23" t="n">
         <v>10</v>
       </c>
+      <c r="AI23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3091,6 +4186,51 @@
       <c r="AH24" t="n">
         <v>200</v>
       </c>
+      <c r="AI24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3197,6 +4337,51 @@
       <c r="AH25" t="n">
         <v>1000</v>
       </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3303,6 +4488,51 @@
       <c r="AH26" t="n">
         <v>1</v>
       </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3407,6 +4637,51 @@
         <v>9</v>
       </c>
       <c r="AH27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW27" t="n">
         <v>9</v>
       </c>
     </row>

--- a/applications/tracking_disturbance_3species_reinforce/Discover_Molecular_Integrators_REINFORCE.xlsx
+++ b/applications/tracking_disturbance_3species_reinforce/Discover_Molecular_Integrators_REINFORCE.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,11 @@
           <t>2025-09-15 13:49:14</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2025-09-15 19:28:35</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -909,6 +914,11 @@
           <t>https://www.comet.com/maurice-filo/molecular-integrators/e64f49daac3a4bc28d80af1d4c31a23a</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/molecular-integrators/3072284f12aa49588adeabed17667611</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1060,6 +1070,9 @@
       <c r="AW3" t="n">
         <v>5</v>
       </c>
+      <c r="AX3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1211,6 +1224,9 @@
       <c r="AW4" t="n">
         <v>3</v>
       </c>
+      <c r="AX4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1362,6 +1378,9 @@
       <c r="AW5" t="n">
         <v>2</v>
       </c>
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1513,6 +1532,9 @@
       <c r="AW6" t="n">
         <v>1280</v>
       </c>
+      <c r="AX6" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1664,6 +1686,9 @@
       <c r="AW7" t="b">
         <v>0</v>
       </c>
+      <c r="AX7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1815,6 +1840,9 @@
       <c r="AW8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AX8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1966,6 +1994,9 @@
       <c r="AW9" t="n">
         <v>500</v>
       </c>
+      <c r="AX9" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2117,6 +2148,9 @@
       <c r="AW10" t="n">
         <v>5</v>
       </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2268,6 +2302,9 @@
       <c r="AW11" t="n">
         <v>1024</v>
       </c>
+      <c r="AX11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2419,6 +2456,9 @@
       <c r="AW12" t="n">
         <v>10240</v>
       </c>
+      <c r="AX12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2570,6 +2610,9 @@
       <c r="AW13" t="n">
         <v>128</v>
       </c>
+      <c r="AX13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2721,6 +2764,9 @@
       <c r="AW14" t="n">
         <v>50</v>
       </c>
+      <c r="AX14" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2872,6 +2918,9 @@
       <c r="AW15" t="n">
         <v>0.75</v>
       </c>
+      <c r="AX15" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3023,6 +3072,9 @@
       <c r="AW16" t="n">
         <v>5</v>
       </c>
+      <c r="AX16" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3174,6 +3226,9 @@
       <c r="AW17" t="n">
         <v>50</v>
       </c>
+      <c r="AX17" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3325,6 +3380,9 @@
       <c r="AW18" t="n">
         <v>0.95</v>
       </c>
+      <c r="AX18" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3476,6 +3534,9 @@
       <c r="AW19" t="n">
         <v>0</v>
       </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3627,6 +3688,9 @@
       <c r="AW20" t="n">
         <v>1</v>
       </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3778,6 +3842,9 @@
       <c r="AW21" t="n">
         <v>20</v>
       </c>
+      <c r="AX21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3929,6 +3996,9 @@
       <c r="AW22" t="n">
         <v>1</v>
       </c>
+      <c r="AX22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4080,6 +4150,9 @@
       <c r="AW23" t="n">
         <v>10</v>
       </c>
+      <c r="AX23" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4231,6 +4304,9 @@
       <c r="AW24" t="n">
         <v>200</v>
       </c>
+      <c r="AX24" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4382,6 +4458,9 @@
       <c r="AW25" t="n">
         <v>1000</v>
       </c>
+      <c r="AX25" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4533,6 +4612,9 @@
       <c r="AW26" t="n">
         <v>1</v>
       </c>
+      <c r="AX26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4682,6 +4764,9 @@
         <v>9</v>
       </c>
       <c r="AW27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX27" t="n">
         <v>9</v>
       </c>
     </row>
